--- a/T4_AUC.xlsx
+++ b/T4_AUC.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>Cardboard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -430,7 +430,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4.CB.A</t>
+          <t>4.Cardboard.A</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.FB.A</t>
+          <t>4.Fabric.A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.WO.A</t>
+          <t>4.Wood.A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Styrofoam</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.SF.A</t>
+          <t>4.Styrofoam.A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.AL.A</t>
+          <t>4.Aluminum.A</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>Rubber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.RB.A</t>
+          <t>4.Rubber.A</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>Stainless Steel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.SS.A</t>
+          <t>4.Stainless Steel.A</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.PP.A</t>
+          <t>4.Plastic.A</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4.CB.A</t>
+          <t>4.Cardboard.A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.FB.A</t>
+          <t>4.Fabric.A</t>
         </is>
       </c>
       <c r="C2">
@@ -858,12 +858,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4.CB.A</t>
+          <t>4.Cardboard.A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.WO.A</t>
+          <t>4.Wood.A</t>
         </is>
       </c>
       <c r="C3">
@@ -885,7 +885,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4.CB.A</t>
+          <t>4.Cardboard.A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -912,12 +912,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4.CB.A</t>
+          <t>4.Cardboard.A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.SF.A</t>
+          <t>4.Styrofoam.A</t>
         </is>
       </c>
       <c r="C5">
@@ -939,12 +939,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4.CB.A</t>
+          <t>4.Cardboard.A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.AL.A</t>
+          <t>4.Aluminum.A</t>
         </is>
       </c>
       <c r="C6">
@@ -966,12 +966,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4.CB.A</t>
+          <t>4.Cardboard.A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.RB.A</t>
+          <t>4.Rubber.A</t>
         </is>
       </c>
       <c r="C7">
@@ -993,12 +993,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4.CB.A</t>
+          <t>4.Cardboard.A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.SS.A</t>
+          <t>4.Stainless Steel.A</t>
         </is>
       </c>
       <c r="C8">
@@ -1020,12 +1020,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4.CB.A</t>
+          <t>4.Cardboard.A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.PP.A</t>
+          <t>4.Plastic.A</t>
         </is>
       </c>
       <c r="C9">
@@ -1047,7 +1047,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4.CB.A</t>
+          <t>4.Cardboard.A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1074,12 +1074,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4.FB.A</t>
+          <t>4.Fabric.A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.WO.A</t>
+          <t>4.Wood.A</t>
         </is>
       </c>
       <c r="C11">
@@ -1101,7 +1101,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4.FB.A</t>
+          <t>4.Fabric.A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1128,12 +1128,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4.FB.A</t>
+          <t>4.Fabric.A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.SF.A</t>
+          <t>4.Styrofoam.A</t>
         </is>
       </c>
       <c r="C13">
@@ -1155,12 +1155,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4.FB.A</t>
+          <t>4.Fabric.A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.AL.A</t>
+          <t>4.Aluminum.A</t>
         </is>
       </c>
       <c r="C14">
@@ -1182,12 +1182,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4.FB.A</t>
+          <t>4.Fabric.A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.RB.A</t>
+          <t>4.Rubber.A</t>
         </is>
       </c>
       <c r="C15">
@@ -1209,12 +1209,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4.FB.A</t>
+          <t>4.Fabric.A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.SS.A</t>
+          <t>4.Stainless Steel.A</t>
         </is>
       </c>
       <c r="C16">
@@ -1236,12 +1236,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4.FB.A</t>
+          <t>4.Fabric.A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.PP.A</t>
+          <t>4.Plastic.A</t>
         </is>
       </c>
       <c r="C17">
@@ -1263,7 +1263,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4.FB.A</t>
+          <t>4.Fabric.A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4.WO.A</t>
+          <t>4.Wood.A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4.WO.A</t>
+          <t>4.Wood.A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.SF.A</t>
+          <t>4.Styrofoam.A</t>
         </is>
       </c>
       <c r="C20">
@@ -1344,12 +1344,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4.WO.A</t>
+          <t>4.Wood.A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.AL.A</t>
+          <t>4.Aluminum.A</t>
         </is>
       </c>
       <c r="C21">
@@ -1371,12 +1371,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4.WO.A</t>
+          <t>4.Wood.A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4.RB.A</t>
+          <t>4.Rubber.A</t>
         </is>
       </c>
       <c r="C22">
@@ -1398,12 +1398,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4.WO.A</t>
+          <t>4.Wood.A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.SS.A</t>
+          <t>4.Stainless Steel.A</t>
         </is>
       </c>
       <c r="C23">
@@ -1425,12 +1425,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4.WO.A</t>
+          <t>4.Wood.A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.PP.A</t>
+          <t>4.Plastic.A</t>
         </is>
       </c>
       <c r="C24">
@@ -1452,7 +1452,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4.WO.A</t>
+          <t>4.Wood.A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4.SF.A</t>
+          <t>4.Styrofoam.A</t>
         </is>
       </c>
       <c r="C26">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4.AL.A</t>
+          <t>4.Aluminum.A</t>
         </is>
       </c>
       <c r="C27">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4.RB.A</t>
+          <t>4.Rubber.A</t>
         </is>
       </c>
       <c r="C28">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4.SS.A</t>
+          <t>4.Stainless Steel.A</t>
         </is>
       </c>
       <c r="C29">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4.PP.A</t>
+          <t>4.Plastic.A</t>
         </is>
       </c>
       <c r="C30">
@@ -1641,12 +1641,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4.SF.A</t>
+          <t>4.Styrofoam.A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4.AL.A</t>
+          <t>4.Aluminum.A</t>
         </is>
       </c>
       <c r="C32">
@@ -1668,12 +1668,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4.SF.A</t>
+          <t>4.Styrofoam.A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4.RB.A</t>
+          <t>4.Rubber.A</t>
         </is>
       </c>
       <c r="C33">
@@ -1695,12 +1695,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4.SF.A</t>
+          <t>4.Styrofoam.A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4.SS.A</t>
+          <t>4.Stainless Steel.A</t>
         </is>
       </c>
       <c r="C34">
@@ -1722,12 +1722,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4.SF.A</t>
+          <t>4.Styrofoam.A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4.PP.A</t>
+          <t>4.Plastic.A</t>
         </is>
       </c>
       <c r="C35">
@@ -1749,7 +1749,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4.SF.A</t>
+          <t>4.Styrofoam.A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1776,12 +1776,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4.AL.A</t>
+          <t>4.Aluminum.A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4.RB.A</t>
+          <t>4.Rubber.A</t>
         </is>
       </c>
       <c r="C37">
@@ -1803,12 +1803,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4.AL.A</t>
+          <t>4.Aluminum.A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4.SS.A</t>
+          <t>4.Stainless Steel.A</t>
         </is>
       </c>
       <c r="C38">
@@ -1830,12 +1830,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4.AL.A</t>
+          <t>4.Aluminum.A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4.PP.A</t>
+          <t>4.Plastic.A</t>
         </is>
       </c>
       <c r="C39">
@@ -1857,7 +1857,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4.AL.A</t>
+          <t>4.Aluminum.A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1884,12 +1884,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4.RB.A</t>
+          <t>4.Rubber.A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4.SS.A</t>
+          <t>4.Stainless Steel.A</t>
         </is>
       </c>
       <c r="C41">
@@ -1911,12 +1911,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4.RB.A</t>
+          <t>4.Rubber.A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4.PP.A</t>
+          <t>4.Plastic.A</t>
         </is>
       </c>
       <c r="C42">
@@ -1938,7 +1938,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4.RB.A</t>
+          <t>4.Rubber.A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4.SS.A</t>
+          <t>4.Stainless Steel.A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4.PP.A</t>
+          <t>4.Plastic.A</t>
         </is>
       </c>
       <c r="C44">
@@ -1992,7 +1992,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4.SS.A</t>
+          <t>4.Stainless Steel.A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4.PP.A</t>
+          <t>4.Plastic.A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>Cardboard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4.CB.B</t>
+          <t>4.Cardboard.B</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.AL.B</t>
+          <t>4.Aluminum.B</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>Stainless Steel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.SS.B</t>
+          <t>4.Stainless Steel.B</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>Rubber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.RB.B</t>
+          <t>4.Rubber.B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.FB.B</t>
+          <t>4.Fabric.B</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Styrofoam</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.SF.B</t>
+          <t>4.Styrofoam.B</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.WO.B</t>
+          <t>4.Wood.B</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.PP.B</t>
+          <t>4.Plastic.B</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2525,12 +2525,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4.CB.B</t>
+          <t>4.Cardboard.B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.AL.B</t>
+          <t>4.Aluminum.B</t>
         </is>
       </c>
       <c r="C2">
@@ -2552,12 +2552,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4.CB.B</t>
+          <t>4.Cardboard.B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.SS.B</t>
+          <t>4.Stainless Steel.B</t>
         </is>
       </c>
       <c r="C3">
@@ -2579,12 +2579,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4.CB.B</t>
+          <t>4.Cardboard.B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.RB.B</t>
+          <t>4.Rubber.B</t>
         </is>
       </c>
       <c r="C4">
@@ -2606,12 +2606,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4.CB.B</t>
+          <t>4.Cardboard.B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.FB.B</t>
+          <t>4.Fabric.B</t>
         </is>
       </c>
       <c r="C5">
@@ -2633,12 +2633,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4.CB.B</t>
+          <t>4.Cardboard.B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.SF.B</t>
+          <t>4.Styrofoam.B</t>
         </is>
       </c>
       <c r="C6">
@@ -2660,12 +2660,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4.CB.B</t>
+          <t>4.Cardboard.B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.WO.B</t>
+          <t>4.Wood.B</t>
         </is>
       </c>
       <c r="C7">
@@ -2687,7 +2687,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4.CB.B</t>
+          <t>4.Cardboard.B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2714,12 +2714,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4.CB.B</t>
+          <t>4.Cardboard.B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.PP.B</t>
+          <t>4.Plastic.B</t>
         </is>
       </c>
       <c r="C9">
@@ -2741,7 +2741,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4.CB.B</t>
+          <t>4.Cardboard.B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2768,12 +2768,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4.AL.B</t>
+          <t>4.Aluminum.B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.SS.B</t>
+          <t>4.Stainless Steel.B</t>
         </is>
       </c>
       <c r="C11">
@@ -2795,12 +2795,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4.AL.B</t>
+          <t>4.Aluminum.B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4.RB.B</t>
+          <t>4.Rubber.B</t>
         </is>
       </c>
       <c r="C12">
@@ -2822,12 +2822,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4.AL.B</t>
+          <t>4.Aluminum.B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.FB.B</t>
+          <t>4.Fabric.B</t>
         </is>
       </c>
       <c r="C13">
@@ -2849,12 +2849,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4.AL.B</t>
+          <t>4.Aluminum.B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.SF.B</t>
+          <t>4.Styrofoam.B</t>
         </is>
       </c>
       <c r="C14">
@@ -2876,12 +2876,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4.AL.B</t>
+          <t>4.Aluminum.B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.WO.B</t>
+          <t>4.Wood.B</t>
         </is>
       </c>
       <c r="C15">
@@ -2903,7 +2903,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4.AL.B</t>
+          <t>4.Aluminum.B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2930,12 +2930,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4.AL.B</t>
+          <t>4.Aluminum.B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.PP.B</t>
+          <t>4.Plastic.B</t>
         </is>
       </c>
       <c r="C17">
@@ -2957,7 +2957,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4.AL.B</t>
+          <t>4.Aluminum.B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2984,12 +2984,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4.SS.B</t>
+          <t>4.Stainless Steel.B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4.RB.B</t>
+          <t>4.Rubber.B</t>
         </is>
       </c>
       <c r="C19">
@@ -3011,12 +3011,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4.SS.B</t>
+          <t>4.Stainless Steel.B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.FB.B</t>
+          <t>4.Fabric.B</t>
         </is>
       </c>
       <c r="C20">
@@ -3038,12 +3038,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4.SS.B</t>
+          <t>4.Stainless Steel.B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.SF.B</t>
+          <t>4.Styrofoam.B</t>
         </is>
       </c>
       <c r="C21">
@@ -3065,12 +3065,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4.SS.B</t>
+          <t>4.Stainless Steel.B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4.WO.B</t>
+          <t>4.Wood.B</t>
         </is>
       </c>
       <c r="C22">
@@ -3092,7 +3092,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4.SS.B</t>
+          <t>4.Stainless Steel.B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3119,12 +3119,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4.SS.B</t>
+          <t>4.Stainless Steel.B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.PP.B</t>
+          <t>4.Plastic.B</t>
         </is>
       </c>
       <c r="C24">
@@ -3146,7 +3146,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4.SS.B</t>
+          <t>4.Stainless Steel.B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4.RB.B</t>
+          <t>4.Rubber.B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4.FB.B</t>
+          <t>4.Fabric.B</t>
         </is>
       </c>
       <c r="C26">
@@ -3200,12 +3200,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4.RB.B</t>
+          <t>4.Rubber.B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4.SF.B</t>
+          <t>4.Styrofoam.B</t>
         </is>
       </c>
       <c r="C27">
@@ -3227,12 +3227,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4.RB.B</t>
+          <t>4.Rubber.B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4.WO.B</t>
+          <t>4.Wood.B</t>
         </is>
       </c>
       <c r="C28">
@@ -3254,7 +3254,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4.RB.B</t>
+          <t>4.Rubber.B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3281,12 +3281,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4.RB.B</t>
+          <t>4.Rubber.B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4.PP.B</t>
+          <t>4.Plastic.B</t>
         </is>
       </c>
       <c r="C30">
@@ -3308,7 +3308,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4.RB.B</t>
+          <t>4.Rubber.B</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3335,12 +3335,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4.FB.B</t>
+          <t>4.Fabric.B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4.SF.B</t>
+          <t>4.Styrofoam.B</t>
         </is>
       </c>
       <c r="C32">
@@ -3362,12 +3362,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4.FB.B</t>
+          <t>4.Fabric.B</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4.WO.B</t>
+          <t>4.Wood.B</t>
         </is>
       </c>
       <c r="C33">
@@ -3389,7 +3389,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4.FB.B</t>
+          <t>4.Fabric.B</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3416,12 +3416,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4.FB.B</t>
+          <t>4.Fabric.B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4.PP.B</t>
+          <t>4.Plastic.B</t>
         </is>
       </c>
       <c r="C35">
@@ -3443,7 +3443,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4.FB.B</t>
+          <t>4.Fabric.B</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3470,12 +3470,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4.SF.B</t>
+          <t>4.Styrofoam.B</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4.WO.B</t>
+          <t>4.Wood.B</t>
         </is>
       </c>
       <c r="C37">
@@ -3497,7 +3497,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4.SF.B</t>
+          <t>4.Styrofoam.B</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3524,12 +3524,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4.SF.B</t>
+          <t>4.Styrofoam.B</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4.PP.B</t>
+          <t>4.Plastic.B</t>
         </is>
       </c>
       <c r="C39">
@@ -3551,7 +3551,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4.SF.B</t>
+          <t>4.Styrofoam.B</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3578,7 +3578,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4.WO.B</t>
+          <t>4.Wood.B</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3605,12 +3605,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4.WO.B</t>
+          <t>4.Wood.B</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4.PP.B</t>
+          <t>4.Plastic.B</t>
         </is>
       </c>
       <c r="C42">
@@ -3632,7 +3632,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4.WO.B</t>
+          <t>4.Wood.B</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4.PP.B</t>
+          <t>4.Plastic.B</t>
         </is>
       </c>
       <c r="C44">
@@ -3713,7 +3713,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4.PP.B</t>
+          <t>4.Plastic.B</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3792,7 +3792,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4.NL.A</t>
+          <t>4.Nasal Lavage.A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>Nasal Lavage</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4.NL.B</t>
+          <t>4.Nasal Lavage.B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>Nasal Lavage</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3991,12 +3991,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4.NL.A</t>
+          <t>4.Nasal Lavage.A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.NL.B</t>
+          <t>4.Nasal Lavage.B</t>
         </is>
       </c>
       <c r="C2">
@@ -4018,7 +4018,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4.NL.A</t>
+          <t>4.Nasal Lavage.A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4045,7 +4045,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4.NL.A</t>
+          <t>4.Nasal Lavage.A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4072,7 +4072,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4.NL.B</t>
+          <t>4.Nasal Lavage.B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4099,7 +4099,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4.NL.B</t>
+          <t>4.Nasal Lavage.B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
